--- a/cypress/fixtures/SkavaMessageContracts.xlsx
+++ b/cypress/fixtures/SkavaMessageContracts.xlsx
@@ -6,6 +6,9 @@
     <sheet state="visible" name="YLAccountUpdated" sheetId="1" r:id="rId4"/>
     <sheet state="visible" name="SkavaAccountCreated" sheetId="2" r:id="rId5"/>
     <sheet state="visible" name="SkavaAccountModified" sheetId="3" r:id="rId6"/>
+    <sheet state="visible" name="OrderPlaced" sheetId="4" r:id="rId7"/>
+    <sheet state="visible" name="OrderReturned" sheetId="5" r:id="rId8"/>
+    <sheet state="visible" name="OrderShipped " sheetId="6" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr/>
@@ -13,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="497" uniqueCount="141">
   <si>
     <t>Name</t>
   </si>
@@ -199,13 +202,250 @@
   </si>
   <si>
     <t>ReactivationDate</t>
+  </si>
+  <si>
+    <t>orderId</t>
+  </si>
+  <si>
+    <t>orderDateTime</t>
+  </si>
+  <si>
+    <t>commissionDate</t>
+  </si>
+  <si>
+    <t>datePaymentSuccessed</t>
+  </si>
+  <si>
+    <t>isoCurrencyCode</t>
+  </si>
+  <si>
+    <t>orderSource</t>
+  </si>
+  <si>
+    <t>checkedBrandPartnerAgreement</t>
+  </si>
+  <si>
+    <t>checkoutAsBrandPartner</t>
+  </si>
+  <si>
+    <t>referenceId</t>
+  </si>
+  <si>
+    <t>orderItems</t>
+  </si>
+  <si>
+    <t>array</t>
+  </si>
+  <si>
+    <t>partNumber</t>
+  </si>
+  <si>
+    <t>quantity</t>
+  </si>
+  <si>
+    <t>salesPriceAmount</t>
+  </si>
+  <si>
+    <t>decimal</t>
+  </si>
+  <si>
+    <t>taxableAmount</t>
+  </si>
+  <si>
+    <t>taxRate</t>
+  </si>
+  <si>
+    <t>personalVolume</t>
+  </si>
+  <si>
+    <t>salesTax</t>
+  </si>
+  <si>
+    <t>amount</t>
+  </si>
+  <si>
+    <t>discounts</t>
+  </si>
+  <si>
+    <t>giftItem</t>
+  </si>
+  <si>
+    <t>donationItem</t>
+  </si>
+  <si>
+    <t>paymentMethodType</t>
+  </si>
+  <si>
+    <t>yes/no</t>
+  </si>
+  <si>
+    <t>shippingAmount</t>
+  </si>
+  <si>
+    <t>shippingTax</t>
+  </si>
+  <si>
+    <t>DeliveryFee</t>
+  </si>
+  <si>
+    <t>subTotal</t>
+  </si>
+  <si>
+    <t>discountsTotal</t>
+  </si>
+  <si>
+    <t>salesTaxTotal</t>
+  </si>
+  <si>
+    <t>total</t>
+  </si>
+  <si>
+    <t>shipping</t>
+  </si>
+  <si>
+    <t>shippingMethodId</t>
+  </si>
+  <si>
+    <t>recipient</t>
+  </si>
+  <si>
+    <t>address</t>
+  </si>
+  <si>
+    <t>line1</t>
+  </si>
+  <si>
+    <t>line2</t>
+  </si>
+  <si>
+    <t>line3</t>
+  </si>
+  <si>
+    <t>city</t>
+  </si>
+  <si>
+    <t>stateProvince</t>
+  </si>
+  <si>
+    <t>postalCode</t>
+  </si>
+  <si>
+    <t>country</t>
+  </si>
+  <si>
+    <t>ylCustomerId</t>
+  </si>
+  <si>
+    <t>customerTaxType</t>
+  </si>
+  <si>
+    <t>ylCustomerIdlongyes</t>
+  </si>
+  <si>
+    <t>donationAmount</t>
+  </si>
+  <si>
+    <t>donationProgramId</t>
+  </si>
+  <si>
+    <t>isException</t>
+  </si>
+  <si>
+    <t>payments</t>
+  </si>
+  <si>
+    <t>isoCountryCode</t>
+  </si>
+  <si>
+    <t>ylPaymentMethodId</t>
+  </si>
+  <si>
+    <t>walletId</t>
+  </si>
+  <si>
+    <t>paymentTransactionId</t>
+  </si>
+  <si>
+    <t>agreement</t>
+  </si>
+  <si>
+    <t>version</t>
+  </si>
+  <si>
+    <t>language</t>
+  </si>
+  <si>
+    <t>url</t>
+  </si>
+  <si>
+    <t>DEPRECATED</t>
+  </si>
+  <si>
+    <t>isPayPal</t>
+  </si>
+  <si>
+    <t>isApplePay</t>
+  </si>
+  <si>
+    <t>isCash</t>
+  </si>
+  <si>
+    <t>isCashCredit</t>
+  </si>
+  <si>
+    <t>tcVersion</t>
+  </si>
+  <si>
+    <t>originalOrderId</t>
+  </si>
+  <si>
+    <t>originalYLOrderId</t>
+  </si>
+  <si>
+    <t>returnId</t>
+  </si>
+  <si>
+    <t>Discounts</t>
+  </si>
+  <si>
+    <t>description</t>
+  </si>
+  <si>
+    <t>returnFees</t>
+  </si>
+  <si>
+    <t>restockingFee</t>
+  </si>
+  <si>
+    <t>handlingFee</t>
+  </si>
+  <si>
+    <t>customFee</t>
+  </si>
+  <si>
+    <t>skavaOrderId</t>
+  </si>
+  <si>
+    <t>shipmentId</t>
+  </si>
+  <si>
+    <t>itemDescription</t>
+  </si>
+  <si>
+    <t>trackingInfo</t>
+  </si>
+  <si>
+    <t>trackingNumber</t>
+  </si>
+  <si>
+    <t>trackingLink</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="6">
+  <fonts count="8">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -239,8 +479,19 @@
       <color rgb="FFFF0000"/>
       <name val="-apple-system"/>
     </font>
+    <font>
+      <sz val="11.0"/>
+      <color rgb="FF1D1C1D"/>
+      <name val="-apple-system"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11.0"/>
+      <color rgb="FF172B4D"/>
+      <name val="-apple-system"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -253,8 +504,20 @@
         <bgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF0B3"/>
+        <bgColor rgb="FFFFF0B3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0F0F0"/>
+        <bgColor rgb="FFF0F0F0"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border/>
     <border>
       <left style="thin">
@@ -270,11 +533,25 @@
         <color rgb="FFDDDDDD"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFDDDDDD"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFDDDDDD"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFDDDDDD"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFFFC400"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="12">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -299,6 +576,18 @@
     <xf borderId="1" fillId="2" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" vertical="top"/>
     </xf>
+    <xf borderId="1" fillId="2" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" vertical="top"/>
+    </xf>
+    <xf borderId="2" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" vertical="top"/>
+    </xf>
+    <xf borderId="1" fillId="4" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" vertical="top"/>
+    </xf>
+    <xf borderId="1" fillId="4" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle xfId="0" name="Normal" builtinId="0"/>
@@ -316,6 +605,18 @@
 </file>
 
 <file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
 </file>
 
@@ -1230,4 +1531,1308 @@
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <cols>
+    <col customWidth="1" min="1" max="1" width="27.75"/>
+    <col customWidth="1" min="2" max="2" width="12.25"/>
+    <col customWidth="1" min="3" max="3" width="10.75"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" s="6"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="6"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="C11" s="6"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="C15" s="6"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="C17" s="6"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="C18" s="6"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="C19" s="6"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="C20" s="6"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="C21" s="6"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C22" s="6"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C23" s="6"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C24" s="5" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="C25" s="6"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="C26" s="6"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="C28" s="5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="C29" s="6"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="C30" s="6"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="C31" s="6"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="B32" s="6"/>
+      <c r="C32" s="6"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="C33" s="5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="B34" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C34" s="5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="B35" s="6"/>
+      <c r="C35" s="6"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="B36" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C36" s="5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="B37" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C37" s="6"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="B38" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C38" s="6"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="B39" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C39" s="5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="B40" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C40" s="5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="B41" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C41" s="5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="B42" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C42" s="5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="B43" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C43" s="5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="B44" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="C44" s="5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="B45" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C45" s="5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="B46" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C46" s="5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="B47" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="C47" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="B48" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="C48" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="B49" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C49" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="9" t="s">
+        <v>111</v>
+      </c>
+      <c r="B50" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="C50" s="6"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="B51" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C51" s="5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="B52" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C52" s="5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="B53" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="C53" s="5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="B54" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C54" s="5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="B55" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C55" s="5" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="B56" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C56" s="5" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="B57" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C57" s="5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="B58" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C58" s="5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="B59" s="6"/>
+      <c r="C59" s="6"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="B60" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C60" s="5" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="B61" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C61" s="5" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="B62" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C62" s="5" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="10" t="s">
+        <v>120</v>
+      </c>
+      <c r="B63" s="11"/>
+      <c r="C63" s="11"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="B64" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C64" s="5" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="B65" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C65" s="5" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="B66" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C66" s="5" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="B67" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C67" s="5" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="B68" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C68" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+  </sheetData>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <cols>
+    <col customWidth="1" min="1" max="1" width="19.13"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="C7" s="6"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="C11" s="6"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="C12" s="6"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="C13" s="6"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="C14" s="6"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="C16" s="6"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C17" s="6"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="C18" s="6"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="C19" s="6"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="C20" s="6"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C21" s="6"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="C22" s="6"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="C23" s="6"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="C24" s="6"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="C25" s="6"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C26" s="5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="C28" s="5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C29" s="5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C30" s="5" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C31" s="5" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="B32" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C32" s="5" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C33" s="5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="B34" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="C34" s="6"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="B35" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="C35" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="B36" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="C36" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="B37" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="C37" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="10" t="s">
+        <v>120</v>
+      </c>
+      <c r="B38" s="11"/>
+      <c r="C38" s="11"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="B39" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C39" s="5" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="B40" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C40" s="5" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="B41" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C41" s="5" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="B42" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C42" s="5" t="s">
+        <v>86</v>
+      </c>
+    </row>
+  </sheetData>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <cols>
+    <col customWidth="1" min="1" max="1" width="13.88"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="C6" s="6"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="s">
+        <v>137</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="6"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="C11" s="6"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+  </sheetData>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>